--- a/artfynd/A 49747-2025 artfynd.xlsx
+++ b/artfynd/A 49747-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112276529</v>
       </c>
       <c r="B2" t="n">
-        <v>99009</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112276528</v>
+        <v>112276534</v>
       </c>
       <c r="B3" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626193</v>
+        <v>626066</v>
       </c>
       <c r="R3" t="n">
-        <v>7023751</v>
+        <v>7023918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112276523</v>
+        <v>112276528</v>
       </c>
       <c r="B4" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112276534</v>
+        <v>112276533</v>
       </c>
       <c r="B5" t="n">
-        <v>94095</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,7 +1001,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626065</v>
+        <v>626066</v>
       </c>
       <c r="R5" t="n">
         <v>7023918</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112276533</v>
+        <v>112276538</v>
       </c>
       <c r="B6" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626065</v>
+        <v>626050</v>
       </c>
       <c r="R6" t="n">
-        <v>7023918</v>
+        <v>7024002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112276538</v>
+        <v>112276523</v>
       </c>
       <c r="B7" t="n">
-        <v>78778</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626049</v>
+        <v>626193</v>
       </c>
       <c r="R7" t="n">
-        <v>7024003</v>
+        <v>7023751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 49747-2025 artfynd.xlsx
+++ b/artfynd/A 49747-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276534</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276528</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276533</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276538</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112276523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>